--- a/training_result/90/0/ar/parameters_4.xlsx
+++ b/training_result/90/0/ar/parameters_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8949</v>
+        <v>0.9623</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9393</v>
+        <v>0.9538</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8399</v>
+        <v>0.8411</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7655</v>
+        <v>0.7695</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9221</v>
+        <v>0.9184</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8319</v>
+        <v>0.8298</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2111</v>
+        <v>0.251</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8829</v>
+        <v>0.879</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9375</v>
+        <v>0.9634</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8903</v>
+        <v>0.8889</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3104</v>
+        <v>0.3123</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9916</v>
+        <v>0.9815</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5855</v>
+        <v>0.586</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7688</v>
+        <v>0.8595</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9731</v>
+        <v>0.9326</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4885</v>
+        <v>0.4886</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6882</v>
+        <v>0.6902</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6214</v>
+        <v>0.622</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.623</v>
+        <v>0.9508</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9313</v>
+        <v>0.916</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.9678</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5743</v>
+        <v>0.5794</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9322</v>
+        <v>0.9061</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8959</v>
+        <v>0.9114</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4228</v>
+        <v>0.4225</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6733</v>
+        <v>0.6735</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.2989</v>
+        <v>0.2988</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1398,13 +1398,91 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>第26站-other</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>第27站-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>第27站-2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>第27站-other</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>第28站-1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>第28站-2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>第28站-other</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
         <v>0</v>
       </c>
     </row>
